--- a/artfynd/A 28070-2023 artfynd.xlsx
+++ b/artfynd/A 28070-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28070-2023 artfynd.xlsx
+++ b/artfynd/A 28070-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103659853</v>
+        <v>103659854</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406257.2145360444</v>
+        <v>406259</v>
       </c>
       <c r="R2" t="n">
-        <v>6771197.692541462</v>
+        <v>6771188</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>103659856</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406340.6943302798</v>
+        <v>406340</v>
       </c>
       <c r="R3" t="n">
-        <v>6771107.812109341</v>
+        <v>6771108</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,50 +870,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103659854</v>
+        <v>103659850</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näsvallen, Dlr</t>
+          <t>Näsvallsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406258.4119328674</v>
+        <v>406164</v>
       </c>
       <c r="R4" t="n">
-        <v>6771187.974009749</v>
+        <v>6771180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,19 +938,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,12 +970,7 @@
         <v>103659852</v>
       </c>
       <c r="B5" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406255.4167871346</v>
+        <v>406255</v>
       </c>
       <c r="R5" t="n">
-        <v>6771203.067955002</v>
+        <v>6771203</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,19 +1035,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103659855</v>
+        <v>103659853</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406340.6943302798</v>
+        <v>406257</v>
       </c>
       <c r="R6" t="n">
-        <v>6771107.812109341</v>
+        <v>6771198</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,24 +1132,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,50 +1161,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103659850</v>
+        <v>103659855</v>
       </c>
       <c r="B7" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näsvallsmyran, Dlr</t>
+          <t>Näsvallen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406163.6006748446</v>
+        <v>406340</v>
       </c>
       <c r="R7" t="n">
-        <v>6771179.835877077</v>
+        <v>6771108</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,19 +1229,14 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 28070-2023 artfynd.xlsx
+++ b/artfynd/A 28070-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659856</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,8 +1290,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103659855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>